--- a/public/templates/mau_ket_qua_hoc_phan.xlsx
+++ b/public/templates/mau_ket_qua_hoc_phan.xlsx
@@ -11,11 +11,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>mssv</t>
   </si>
   <si>
+    <t>ho_dem</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>ma_lop_hoc_phan</t>
+  </si>
+  <si>
     <t>ma_hoc_phan</t>
   </si>
   <si>
@@ -25,61 +34,73 @@
     <t>so_tin_chi</t>
   </si>
   <si>
-    <t>diem_qua_trinh</t>
-  </si>
-  <si>
-    <t>diem_thi</t>
-  </si>
-  <si>
-    <t>diem_tong_ket</t>
+    <t>diem_thuong_xuyen</t>
+  </si>
+  <si>
+    <t>duoc_du_thi</t>
+  </si>
+  <si>
+    <t>diem_cuoi_ky</t>
+  </si>
+  <si>
+    <t>vang_thi</t>
+  </si>
+  <si>
+    <t>thang_diem_4</t>
   </si>
   <si>
     <t>diem_chu</t>
   </si>
   <si>
-    <t>ket_qua</t>
-  </si>
-  <si>
     <t>ngay_cong_bo</t>
   </si>
   <si>
-    <t>KTPM2311019</t>
-  </si>
-  <si>
-    <t>KTPM101</t>
-  </si>
-  <si>
-    <t>Cơ sở dữ liệu</t>
-  </si>
-  <si>
-    <t>KTPM2311040</t>
-  </si>
-  <si>
-    <t>KTPM2311023</t>
-  </si>
-  <si>
-    <t>KTPM102</t>
-  </si>
-  <si>
-    <t>Lập trình Web</t>
+    <t>KTPM2411901</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>010100240802</t>
+  </si>
+  <si>
+    <t>Logic học</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>Không</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>KTPM2411902</t>
+  </si>
+  <si>
+    <t>Trần Thị</t>
+  </si>
+  <si>
+    <t>Bích</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>DAT</t>
-  </si>
-  <si>
-    <t>KTPM103</t>
-  </si>
-  <si>
-    <t>Mạng máy tính</t>
+    <t>KTPM2411903</t>
+  </si>
+  <si>
+    <t>Lê Văn</t>
+  </si>
+  <si>
+    <t>Cường</t>
   </si>
   <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>KHONG_DAT</t>
   </si>
 </sst>
 </file>
@@ -467,21 +488,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="2" customWidth="1"/>
+    <col min="1" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="12" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -491,134 +515,161 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>8.5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
         <v>3</v>
       </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="2">
-        <v>46300</v>
+      <c r="M2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2">
+        <v>45977</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>8.3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>3.8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>4.5</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="2">
-        <v>46300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>8.5</v>
-      </c>
-      <c r="G4">
-        <v>8.7</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3.8</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2">
-        <v>46386</v>
+      <c r="K4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="2">
+        <v>45977</v>
       </c>
     </row>
   </sheetData>
